--- a/FREVS/preakness shopping center.xlsx
+++ b/FREVS/preakness shopping center.xlsx
@@ -750,7 +750,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Price inputs — leave blank until you have a price</t>
+          <t>Price inputs — 100% of the center</t>
         </is>
       </c>
       <c r="B20" s="11" t="n"/>
@@ -765,10 +765,12 @@
           <t>LOW sale price, 100% of the center</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n"/>
+      <c r="B21" s="14" t="n">
+        <v>10000000</v>
+      </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Blank. No contract, appraisal, or property NOI in the filings.</t>
+          <t>Entered price for 100% of the center: LOW 10,000,000 and HIGH 25,000,000.</t>
         </is>
       </c>
     </row>
@@ -778,7 +780,9 @@
           <t>HIGH sale price, 100% of the center</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n"/>
+      <c r="B22" s="14" t="n">
+        <v>25000000</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -786,9 +790,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" t="n" s="7">
         <f>IF(B21="","",B21)</f>
-        <v/>
+        <v>10000000</v>
       </c>
     </row>
     <row r="24">
@@ -797,15 +801,15 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" t="n" s="7">
         <f>IF(B22="","",B22)</f>
-        <v/>
+        <v>25000000</v>
       </c>
     </row>
     <row r="26" ht="72" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>LOW and HIGH are blank on purpose. Sibling models capitalize NOI (brooks.xlsx, the hotels) or use a contract. This center has neither a disclosed NOI nor a contract. Holding it at book inside common equity is the investment-case treatment until both price cells above are filled. Do not apply the hotel 9.5% / 10.5% discount rates; those are for the Mayflower and the Courtland Grand, not for a shopping center.</t>
+          <t>LOW is 10,000,000 and HIGH is 25,000,000 for 100% of the center. These prices were entered directly. They are not a cap rate and they are not from a filing. The investment case takes 40% of (price minus carrying value).</t>
         </is>
       </c>
     </row>
@@ -822,9 +826,9 @@
           <t>Ownership</t>
         </is>
       </c>
-      <c r="B101" s="17">
+      <c r="B101" t="n" s="17">
         <f>B5</f>
-        <v/>
+        <v>0.4</v>
       </c>
     </row>
     <row r="102">
@@ -833,9 +837,9 @@
           <t>Book carrying value</t>
         </is>
       </c>
-      <c r="B102" s="18">
+      <c r="B102" t="n" s="18">
         <f>B14</f>
-        <v/>
+        <v>20305000</v>
       </c>
     </row>
     <row r="103">
@@ -844,9 +848,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="B103" s="18">
+      <c r="B103" t="n" s="18">
         <f>B23</f>
-        <v/>
+        <v>10000000</v>
       </c>
     </row>
     <row r="104">
@@ -855,9 +859,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="B104" s="18">
+      <c r="B104" t="n" s="18">
         <f>B24</f>
-        <v/>
+        <v>25000000</v>
       </c>
     </row>
     <row r="105">
@@ -866,9 +870,9 @@
           <t>Estimate flag (1 = use LOW/HIGH, 0 = leave blank and hold at book)</t>
         </is>
       </c>
-      <c r="B105" s="19">
+      <c r="B105" t="n" s="19">
         <f>IF(OR(B21="",B22=""),0,1)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -877,9 +881,9 @@
           <t>Mortgage</t>
         </is>
       </c>
-      <c r="B106" s="18">
+      <c r="B106" t="n" s="18">
         <f>B15</f>
-        <v/>
+        <v>19977000</v>
       </c>
     </row>
     <row r="107">
@@ -898,7 +902,7 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Not estimated. No property NOI, appraisal, or sale contract in the filings. Blank LOW and HIGH. Estate keeps the carrying value that is already in common equity.</t>
+          <t>Entered prices for 100% of the center: LOW 10,000,000 and HIGH 25,000,000. The investment case takes 40% of (price minus carrying value).</t>
         </is>
       </c>
     </row>
